--- a/artfynd/A 32644-2020 artfynd.xlsx
+++ b/artfynd/A 32644-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32644-2020 artfynd.xlsx
+++ b/artfynd/A 32644-2020 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>89042906</v>
       </c>
       <c r="B14" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>367263.0853294471</v>
+        <v>367263</v>
       </c>
       <c r="R14" t="n">
-        <v>6725635.166136926</v>
+        <v>6725635</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,19 +2101,9 @@
           <t>2020-11-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-11-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 32644-2020 artfynd.xlsx
+++ b/artfynd/A 32644-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6518,54 +6518,55 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>89316611</v>
+        <v>89042916</v>
       </c>
       <c r="B54" t="n">
-        <v>96334</v>
+        <v>5135</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bavinasbäcken, Vrm</t>
+          <t>Bavinasbäcken, Sörberget, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>367319.0301567637</v>
+        <v>367264.0331651638</v>
       </c>
       <c r="R54" t="n">
-        <v>6725738.647552177</v>
+        <v>6725620.894146536</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6590,11 +6591,6 @@
           <t>Södra Finnskoga</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>S-Tor-0294</t>
-        </is>
-      </c>
       <c r="Y54" t="inlineStr">
         <is>
           <t>2020-11-10</t>
@@ -6621,14 +6617,13 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -6636,128 +6631,7 @@
           <t>Helena Malmestrand</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>89042916</v>
-      </c>
-      <c r="B55" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Bavinasbäcken, Sörberget, Vrm</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>367264.0331651638</v>
-      </c>
-      <c r="R55" t="n">
-        <v>6725620.894146536</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Södra Finnskoga</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2020-11-10</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2020-11-10</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Helena Malmestrand</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Helena Malmestrand</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
